--- a/05_statistics/paper_level_ai_summary.xlsx
+++ b/05_statistics/paper_level_ai_summary.xlsx
@@ -486,17 +486,17 @@
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>operando/spectroscopy</t>
+          <t>review</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>No included sentence-level pathway evidence after AI review.</t>
+          <t>Only one sentence with 'mention' role and low confidence, not included in statistics; no pathway evidence for ethanol formation.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -518,19 +518,15 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>P1;P5</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>P1;P5</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
           <t>P5</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>yes</t>
@@ -538,17 +534,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>DFT;DFT;operando/spectroscopy;operando/spectroscopy;operando/spectroscopy;product inference;unknown</t>
+          <t>DFT</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sentence-level AI review found main-pathway evidence for P1;P5.</t>
+          <t>本文通过DFT计算详细研究了Cu2-CuN3簇上的CO2RR生成乙醇的机制，主要路径为*OCHO机制生成乙醇，多个句子明确指向乙醇形成，且没有冲突或排除路径。</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -565,10 +561,14 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>P5</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
@@ -577,12 +577,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>DFT;DFT;operando/spectroscopy;operando/spectroscopy;review;unknown</t>
+          <t>spectroscopy</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sentence-level AI review found pathway mentions for P5, but no main-pathway claim.</t>
+          <t>The paper focuses on asymmetric C-C coupling via *OCCOH intermediate to produce ethanol, as evidenced by in-situ ATR-IRAS spectroscopy. Main pathway is P1.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -604,12 +604,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>P1;P2;P5</t>
+          <t>P2;P5</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>P1;P2;P5</t>
+          <t>P2;P5</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -620,17 +620,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>DFT;DFT;operando/spectroscopy;isotope;product inference;unknown</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sentence-level AI review found main-pathway evidence for P1;P2;P5.</t>
+          <t>The paper proposes a tandem catalyst with dual active sites (Sn and O) that enable C-C coupling between *CHO and *CO(OH) (P2) and between formate/HCOOH and *CO(OH) (P5) to form ethanol. Evidence includes DFT calculations, isotope labeling, and product distribution experiments.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -655,12 +655,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>DFT;product inference</t>
+          <t>review</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>No included sentence-level pathway evidence after AI review.</t>
+          <t>No sentence-level evidence with include_in_statistics=yes. Only one sentence reviewed (mention of P3) but excluded. Ethanol specificity unclear; evidence type is review. Overall confidence low due to lack of substantive evidence.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -690,29 +690,25 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>operando/spectroscopy;operando/spectroscopy;product inference;product inference</t>
+          <t>spectroscopy</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sentence-level AI review found main-pathway evidence for P1.</t>
+          <t>The paper focuses on tunable wettability to control *CO and *H coverage for C2+ products, with in-situ ATR-SEIRAS and Raman spectroscopy showing enhanced *CO coverage leads to improved ethylene and ethanol selectivity. No specific ethanol-only pathway is identified; the main pathway (P1) is CO-CO coupling common to both products.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -727,34 +723,22 @@
           <t>ETOH_012</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>P1;P5</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>P5</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>product inference;review</t>
+          <t>DFT</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sentence-level AI review found main-pathway evidence for P5.</t>
+          <t>Only one sentence-level annotation with role 'mention' and include_in_statistics='no'. The paper focuses on methodological description without explicit pathway claims or ethanol specificity.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -764,7 +748,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -774,26 +758,22 @@
           <t>ETOH_014</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
+      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>product inference</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sentence-level AI review found pathway mentions for P1, but no main-pathway claim.</t>
+          <t>No sentence-level reviews available; paper focuses on n-propanol, not ethanol.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -803,7 +783,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -815,33 +795,37 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>P1;P2;P3;P5;P6</t>
+          <t>P1;P3;P6</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>P1;P3;P5</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>P1;P3;P6</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>P6</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>DFT;isotope;DFT;operando/spectroscopy;DFT;operando/spectroscopy;isotope;product inference;DFT;operando/spectroscopy;product inference;DFT;product inference;operando/spectroscopy;operando/spectroscopy;isotope;operando/spectroscopy;product inference;product inference;unknown</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sentence-level AI review found main-pathway evidence for P1;P3;P5.</t>
+          <t>该文献主要基于原位拉曼光谱（SERS）和DFT计算，识别了CO2还原制乙烯和乙醇的关键中间体。统计句显示P1（OCCO路径）、P3（*CHCO→*OCHCH2路径）和P6（*OCHCH路径）是主要提及路径，其中P3和P6明确指向乙醇，P1主要指向乙烯。同时，DFT计算排除了P6（CO-CH耦合）在缺陷位上的主导作用，但实验SERS证实了*OCHCH中间体。因此，文献级路径存在部分冲突，但整体上乙醇路径证据明确。</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -858,12 +842,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>P1;P2;P5</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>P1;P2</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -874,17 +858,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>DFT;operando/spectroscopy;DFT;operando/spectroscopy;isotope;DFT;operando/spectroscopy;isotope;product inference;DFT;operando/spectroscopy;product inference;operando/spectroscopy;operando/spectroscopy;product inference;unknown</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sentence-level AI review found main-pathway evidence for P1;P2.</t>
+          <t>The paper identifies P2 (asymmetric *CO-*CHO coupling) as the main pathway for ethanol formation, supported by DFT, operando spectroscopy, and isotope labeling experiments. No rejected pathways are present.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -899,32 +883,40 @@
           <t>ETOH_023</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>P1;P3;P4</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>P1;P3;P4</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>DFT;operando/spectroscopy;DFT;product inference;operando/spectroscopy;unknown</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>No included sentence-level pathway evidence after AI review.</t>
+          <t>This paper focuses on electrocatalytic CO2 reduction to ethanol via subsurface Co-doped CuS catalyst. The main pathways involve asymmetric C-C coupling (*CO + *COH → *OCCOH) and subsequent hydrogenation steps to ethanol (P1, P3, P4), supported by DFT calculations and in-situ FTIR spectroscopy. Key evidence includes explicit ethanol pathway in S0246 and shared intermediate *CHCHO in S0040.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -936,7 +928,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>P1;P2;P5</t>
+          <t>P1;P2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -944,11 +936,7 @@
           <t>P1;P2</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>P1;P2;P5</t>
-        </is>
-      </c>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>yes</t>
@@ -956,17 +944,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>DFT;operando/spectroscopy;product inference;DFT;product inference;operando/spectroscopy;product inference;product inference</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sentence-level AI review found main-pathway evidence for P1;P2.</t>
+          <t>通过DFT和原位光谱证实CA分子促进*OC2H3中间体C-O键保留，有利于乙醇生成，主要路径为P1和P2。</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -986,17 +974,17 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>DFT;DFT;operando/spectroscopy;operando/spectroscopy</t>
+          <t>DFT</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>No included sentence-level pathway evidence after AI review.</t>
+          <t>No ethanol-specific pathways identified; all evidence is DFT on *CO dimerization/hydrogenation, with no product distribution or ethanol mention.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1016,40 +1004,32 @@
           <t>ETOH_B2_003</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
+      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>P5</t>
-        </is>
-      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>DFT;operando/spectroscopy;operando/spectroscopy;product inference</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sentence-level AI review found pathway mentions for P2, but no main-pathway claim.</t>
+          <t>该文献主要研究Ag掺杂Cu2O纳米立方体催化剂对CO2电还原至C2+液体产物的增强效果，其中乙醇是产物之一。句子级分析中，所有提及乙醇路径的句子均未被纳入统计（ai_include_in_statistics=no），且这些路径（CO spillover、*CO-*CH耦合）均来自文献引用或推断，缺乏直接的实验或理论证据支持。因此，无法确定该文献的主要乙醇形成路径，也无明确排除的路径。文献整体对乙醇的特异性程度较低，因为乙醇只是多种C2+液体产物之一，且证据混杂。因此，文献级判断为不纳入最终统计。</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1049,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>operando/spectroscopy;product inference</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>No included sentence-level pathway evidence after AI review.</t>
+          <t>No sentence-level AI judgments available for this paper.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1094,30 +1074,22 @@
           <t>ETOH_B2_005</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>P5</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>P5</t>
-        </is>
-      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>DFT;operando/spectroscopy;product inference;operando/spectroscopy;product inference</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sentence-level AI review found main-pathway evidence for P5.</t>
+          <t>S0012 mentions orienting reaction pathway towards C2+ products including ethanol and ethylene, but lacks details on ethanol-specific intermediates; S0147 is a general review of CO2RR via *CO dimerization or *CO-COH intermediate. No sentence provides specific ethanol pathway evidence. Overall, the paper focuses on C2+ products with ambiguous ethanol specificity.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1127,7 +1099,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -1137,36 +1109,40 @@
           <t>ETOH_B2_006</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>DFT;DFT;operando/spectroscopy;operando/spectroscopy;product inference;unknown</t>
+          <t>DFT</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>No included sentence-level pathway evidence after AI review.</t>
+          <t>The paper focuses on C-C coupling on OD-Cu catalysts, with DFT calculations showing that square-like sites stabilize *COCO intermediate (P1). One comparison sentence (S0078) mentions alcohol pathway (including ethanol) but provides no specific pathway details. Overall, evidence is partially ethanol-related but not definitive.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1181,17 +1157,17 @@
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>operando/spectroscopy</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>No included sentence-level pathway evidence after AI review.</t>
+          <t>No sentence-level AI judgments available; paper metadata insufficient for pathway determination.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1211,32 +1187,36 @@
           <t>ETOH_B2_009</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>P5</t>
+        </is>
+      </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>DFT;product inference</t>
+          <t>product distribution</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>No included sentence-level pathway evidence after AI review.</t>
+          <t>P5 is mentioned as a pathway for ethanol formation based on product inference from cation effect study, but no detailed mechanism is provided.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1231,17 @@
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>operando/spectroscopy</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>No included sentence-level pathway evidence after AI review.</t>
+          <t>One sentence-level review with low confidence; sentence describes product analysis method without pathway information; no main or rejected pathways identified.</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1283,19 +1263,15 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>P1;P4;P5</t>
+          <t>P1;P5</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>P1;P5</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
           <t>P1</t>
         </is>
       </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
           <t>yes</t>
@@ -1303,17 +1279,17 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>DFT;DFT;operando/spectroscopy;DFT;product inference;operando/spectroscopy;product inference;unknown</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sentence-level AI review found main-pathway evidence for P1;P5.</t>
+          <t>基于DFT计算和ATR-SEIRAS实验检测到关键中间体*OCCOH和*OCH2CH3，明确支持乙醇生成路径（*OCCOH → *OCHCOH → 乙醇），且与实验观测到的C2+醇高选择性一致。</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1330,33 +1306,29 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
+          <t>P1;P3</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>isotope;product inference</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sentence-level AI review found main-pathway evidence for P1.</t>
+          <t>The paper discusses both P1 (OCCOH pathway via OCHCH*) and P3 (CHCOH pathway) in the context of ethanol/ethylene selectivity, with DFT and review evidence. Sentence S0193 compares barriers for ethylene vs. acetaldehyde from OCHCH* (P1, unclear ethanol-specific), while S0079 mentions competition of CH2CO and CHCOH pathways (P3, ethanol-specific). Overall, ethanol formation is addressed but mixed with general C2+ oxygenates discussion.</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1371,26 +1343,22 @@
           <t>ETOH_B2_015</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>P5</t>
-        </is>
-      </c>
+      <c r="B24" t="inlineStr"/>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>DFT;product inference</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sentence-level AI review found pathway mentions for P5, but no main-pathway claim.</t>
+          <t>论文主要关注醛类产物，乙醇仅作为产物列表提及，缺乏乙醇形成路径的机制证据。句子级判读均被排除在统计之外，未提供乙醇特异性路径信息。</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1400,7 +1368,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -1417,28 +1385,28 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1;P2;P3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>DFT;operando/spectroscopy;DFT;operando/spectroscopy;product inference;DFT;product inference;operando/spectroscopy;operando/spectroscopy;product inference;unknown</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sentence-level AI review found main-pathway evidence for P2.</t>
+          <t>The paper focuses on low-coordinated Cu catalysts for CO2 reduction to C2+ alcohols, primarily ethanol. DFT calculations and operando Raman spectroscopy identify pathways P1 (*OCCOH intermediate via *CO-COH coupling), P2 (*CH2CO intermediate), and P3 (*CO-COH coupling) as main routes. Evidence includes DFT energy barriers and spectroscopic detection of key intermediates (*OCCOH, *CHO, *OCH2CH3). While ethanol is the dominant product (FE ~56%), the paper often refers to C2+ alcohols generally, leading to a partial ethanol-specific level.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">

--- a/05_statistics/paper_level_ai_summary.xlsx
+++ b/05_statistics/paper_level_ai_summary.xlsx
@@ -491,12 +491,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Only one sentence with 'mention' role and low confidence, not included in statistics; no pathway evidence for ethanol formation.</t>
+          <t>Only one sentence-level review available with role mention and low confidence; no main pathways identified.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>本文通过DFT计算详细研究了Cu2-CuN3簇上的CO2RR生成乙醇的机制，主要路径为*OCHO机制生成乙醇，多个句子明确指向乙醇形成，且没有冲突或排除路径。</t>
+          <t>DFT calculations explicitly describe the *OCHO mechanism leading to ethanol formation on Cu2-CuN3 clusters. All main evidence confirms P5 pathway.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>The paper focuses on asymmetric C-C coupling via *OCCOH intermediate to produce ethanol, as evidenced by in-situ ATR-IRAS spectroscopy. Main pathway is P1.</t>
+          <t>The paper's main pathway P1 (asymmetric C-C coupling via *OCCOH) is supported by in-situ ATR-IRAS spectroscopy showing *OCCOH and *OC2H5 intermediates, and the schematic explicitly describes boosted ethanol generation. Although one sentence mentions *CHO intermediate (P2), it is not included in statistics. The evidence consistently points to ethanol formation.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>The paper proposes a tandem catalyst with dual active sites (Sn and O) that enable C-C coupling between *CHO and *CO(OH) (P2) and between formate/HCOOH and *CO(OH) (P5) to form ethanol. Evidence includes DFT calculations, isotope labeling, and product distribution experiments.</t>
+          <t>该文献主要报道了Sn基串联催化剂将CO2还原为乙醇，提出了两种主要路径：P2 (*CHO和*CO(OH)偶联)和P5 (甲酸/碳酸氢盐中间体与CO偶联)。通过DFT计算、同位素标记实验和产物分布分析证实了这些路径，所有证据均明确指向乙醇生成。</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -660,7 +660,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>No sentence-level evidence with include_in_statistics=yes. Only one sentence reviewed (mention of P3) but excluded. Ethanol specificity unclear; evidence type is review. Overall confidence low due to lack of substantive evidence.</t>
+          <t>Only one sentence-level review of previous theoretical work on C-C coupling via COH+CO to HOCCO is mentioned, not as main evidence, and excluded from statistics.</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>The paper focuses on tunable wettability to control *CO and *H coverage for C2+ products, with in-situ ATR-SEIRAS and Raman spectroscopy showing enhanced *CO coverage leads to improved ethylene and ethanol selectivity. No specific ethanol-only pathway is identified; the main pathway (P1) is CO-CO coupling common to both products.</t>
+          <t>The paper focuses on how interfacial wettability affects *CO and *H coverage, thereby influencing pathways to ethylene and ethanol. The main evidence from sentence S0322 correlates *CO coverage with ethanol/ethylene pathways using in-situ spectroscopy, but the study addresses both products, so ethanol is not uniquely identified.</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Only one sentence-level annotation with role 'mention' and include_in_statistics='no'. The paper focuses on methodological description without explicit pathway claims or ethanol specificity.</t>
+          <t>No valid sentence-level pathway evidence with include_in_statistics=yes; the only reviewed sentence is excluded due to low relevance. Overall paper focuses on multi-carbon products without clear ethanol-specific pathway.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>No sentence-level reviews available; paper focuses on n-propanol, not ethanol.</t>
+          <t>No sentence-level judgments available; paper focuses on acetaldehyde branch for n-propanol, not ethanol formation.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -795,12 +795,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>P1;P3;P6</t>
+          <t>P1; P3; P6</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>P1;P3;P6</t>
+          <t>P1; P3; P6</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>该文献主要基于原位拉曼光谱（SERS）和DFT计算，识别了CO2还原制乙烯和乙醇的关键中间体。统计句显示P1（OCCO路径）、P3（*CHCO→*OCHCH2路径）和P6（*OCHCH路径）是主要提及路径，其中P3和P6明确指向乙醇，P1主要指向乙烯。同时，DFT计算排除了P6（CO-CH耦合）在缺陷位上的主导作用，但实验SERS证实了*OCHCH中间体。因此，文献级路径存在部分冲突，但整体上乙醇路径证据明确。</t>
+          <t>Main pathways P1, P3, P6 are supported by operando spectroscopy (Raman/SERS) identifying *OCCO(H), *CHCO reduction to *OCHCH2, and *OCHCH intermediates. However, P6 is also rejected by DFT simulations on distorted sites, creating a conflict. Ethanol is specifically addressed but some P1 evidence relates to ethylene only.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -850,7 +850,11 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>yes</t>
@@ -858,12 +862,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>DFT;isotope;operando/spectroscopy</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>The paper identifies P2 (asymmetric *CO-*CHO coupling) as the main pathway for ethanol formation, supported by DFT, operando spectroscopy, and isotope labeling experiments. No rejected pathways are present.</t>
+          <t>The paper focuses on asymmetric *CO-*CHO coupling as the primary pathway for ethanol formation, supported by DFT calculations, isotopic labeling, and operando spectroscopy. All main evidence sentences explicitly attribute ethanol selectivity to this pathway.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -901,17 +905,17 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>DFT</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>This paper focuses on electrocatalytic CO2 reduction to ethanol via subsurface Co-doped CuS catalyst. The main pathways involve asymmetric C-C coupling (*CO + *COH → *OCCOH) and subsequent hydrogenation steps to ethanol (P1, P3, P4), supported by DFT calculations and in-situ FTIR spectroscopy. Key evidence includes explicit ethanol pathway in S0246 and shared intermediate *CHCHO in S0040.</t>
+          <t>主要基于DFT计算和in-situ FTIR验证，提出了从CO2到乙醇的完整路径，包括*OCCOH不对称偶联和*CHCHO中间体转化。主路径为P1,P3,P4。</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -949,7 +953,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>通过DFT和原位光谱证实CA分子促进*OC2H3中间体C-O键保留，有利于乙醇生成，主要路径为P1和P2。</t>
+          <t>论文通过DFT和原位拉曼光谱确认了*OCCOH和*OC2H5中间体，并在CA存在下促进乙醇生成，因此主要路径为P1和P2。</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -974,7 +978,7 @@
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -984,7 +988,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>No ethanol-specific pathways identified; all evidence is DFT on *CO dimerization/hydrogenation, with no product distribution or ethanol mention.</t>
+          <t>The paper discusses *CO dimerization and hydrogenation pathways based on DFT calculations, but does not specifically address ethanol formation. No ethanol-specific product distribution or isotope labeling is mentioned. All sentence-level evaluations indicate low relevance to ethanol.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1009,17 +1013,17 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>该文献主要研究Ag掺杂Cu2O纳米立方体催化剂对CO2电还原至C2+液体产物的增强效果，其中乙醇是产物之一。句子级分析中，所有提及乙醇路径的句子均未被纳入统计（ai_include_in_statistics=no），且这些路径（CO spillover、*CO-*CH耦合）均来自文献引用或推断，缺乏直接的实验或理论证据支持。因此，无法确定该文献的主要乙醇形成路径，也无明确排除的路径。文献整体对乙醇的特异性程度较低，因为乙醇只是多种C2+液体产物之一，且证据混杂。因此，文献级判断为不纳入最终统计。</t>
+          <t>The paper mentions ethanol formation via CO spillover and *CO-*CH coupling based on literature, but does not provide original main pathway evidence; ethanol is mentioned alongside other C2+ products.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1044,7 +1048,7 @@
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1054,7 +1058,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>No sentence-level AI judgments available for this paper.</t>
+          <t>No sentence-level data available; no pathway evidence identified.</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1079,17 +1083,17 @@
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>partial</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>review</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>S0012 mentions orienting reaction pathway towards C2+ products including ethanol and ethylene, but lacks details on ethanol-specific intermediates; S0147 is a general review of CO2RR via *CO dimerization or *CO-COH intermediate. No sentence provides specific ethanol pathway evidence. Overall, the paper focuses on C2+ products with ambiguous ethanol specificity.</t>
+          <t>Only mention-level sentences with 'include_in_statistics=no', no main or compare pathways; evidence is primarily review-type with low confidence on ethanol specificity.</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1127,17 +1131,17 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>DFT</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>The paper focuses on C-C coupling on OD-Cu catalysts, with DFT calculations showing that square-like sites stabilize *COCO intermediate (P1). One comparison sentence (S0078) mentions alcohol pathway (including ethanol) but provides no specific pathway details. Overall, evidence is partially ethanol-related but not definitive.</t>
+          <t>Main pathway is CO dimerization (P1) based on DFT calculations and product distribution inferences. Some sentences mention ethanol formation but lack detailed pathways, leading to partial ethanol specificity. Overall evidence strength and specificity are limited.</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1152,12 +1156,24 @@
           <t>ETOH_B2_007</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1167,7 +1183,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>No sentence-level AI judgments available; paper metadata insufficient for pathway determination.</t>
+          <t>No sentence-level reviews available; metadata insufficient to determine pathways.</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1196,7 +1212,7 @@
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1206,12 +1222,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>P5 is mentioned as a pathway for ethanol formation based on product inference from cation effect study, but no detailed mechanism is provided.</t>
+          <t>The paper only mentions ethanol formation in the context of cation effects on product distribution, but does not provide detailed mechanism. It is a review paper.</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1241,7 +1257,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>One sentence-level review with low confidence; sentence describes product analysis method without pathway information; no main or rejected pathways identified.</t>
+          <t>仅有描述分析方法，无相关路径讨论</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1284,12 +1300,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>基于DFT计算和ATR-SEIRAS实验检测到关键中间体*OCCOH和*OCH2CH3，明确支持乙醇生成路径（*OCCOH → *OCHCOH → 乙醇），且与实验观测到的C2+醇高选择性一致。</t>
+          <t>主路径为P1（乙醇），通过DFT计算和ATR-SEIRAS光谱检测关键中间体*OCCOH和*OCH2CH3得到支持；同时提及P5（C2+产物）作为次要路径。无排除路径。</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1318,12 +1334,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>DFT</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>The paper discusses both P1 (OCCOH pathway via OCHCH*) and P3 (CHCOH pathway) in the context of ethanol/ethylene selectivity, with DFT and review evidence. Sentence S0193 compares barriers for ethylene vs. acetaldehyde from OCHCH* (P1, unclear ethanol-specific), while S0079 mentions competition of CH2CO and CHCOH pathways (P3, ethanol-specific). Overall, ethanol formation is addressed but mixed with general C2+ oxygenates discussion.</t>
+          <t>主要基于DFT计算比较了从CHCO*中间体分叉的路径，其中CHCOH路径（P3）与乙醇生成相关，但文章中同时也讨论了乙烯和乙酸，乙醇特异性证据不充分，属于部分提及。</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1358,7 +1374,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>论文主要关注醛类产物，乙醇仅作为产物列表提及，缺乏乙醇形成路径的机制证据。句子级判读均被排除在统计之外，未提供乙醇特异性路径信息。</t>
+          <t>Only mentions of ethanol as a product without mechanistic details; no pathway evidence.</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1401,7 +1417,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>The paper focuses on low-coordinated Cu catalysts for CO2 reduction to C2+ alcohols, primarily ethanol. DFT calculations and operando Raman spectroscopy identify pathways P1 (*OCCOH intermediate via *CO-COH coupling), P2 (*CH2CO intermediate), and P3 (*CO-COH coupling) as main routes. Evidence includes DFT energy barriers and spectroscopic detection of key intermediates (*OCCOH, *CHO, *OCH2CH3). While ethanol is the dominant product (FE ~56%), the paper often refers to C2+ alcohols generally, leading to a partial ethanol-specific level.</t>
+          <t>The paper presents DFT calculations and operando Raman spectroscopy to elucidate pathways for CO2 reduction to C2+ alcohols on Cu/Cu2O catalysts. Key evidence supports *CO-COH coupling (P3) and *OCCOH intermediate (P1) for ethanol formation, with minor mention of *CH2CO affinity (P2). Although ethanol is a major product (FE ~56%), some evidence is generalized to C2+ alcohols, leading to partial ethanol specificity.</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
